--- a/data/raw/male_life_table_southeast_brazil_2025.xlsx
+++ b/data/raw/male_life_table_southeast_brazil_2025.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6671f81417a0f489/Documentos/Projeto IC - Vanessa/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6671f81417a0f489/Documentos/projeto_longevidade/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_F25DC773A252ABDACC104828F1DA7B125ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{939E0497-A90D-4CE6-AFA4-F03463C62205}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_F25DC773A252ABDACC104828F1DA7B125ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8BEAD668-376B-4011-94ED-46AEB2ED7D63}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -516,31 +516,31 @@
         <v>0</v>
       </c>
       <c r="B2" s="4">
-        <v>1.22462564778441E-2</v>
+        <v>1.26536104536169E-2</v>
       </c>
       <c r="C2" s="4">
-        <v>7.7314601798816898E-2</v>
+        <v>7.8459809526490995E-2</v>
       </c>
       <c r="D2" s="4">
-        <v>1.21094267126309E-2</v>
+        <v>1.2507759835302199E-2</v>
       </c>
       <c r="E2" s="5">
         <v>100000</v>
       </c>
       <c r="F2" s="5">
-        <v>1210.94267126308</v>
+        <v>1250.77598353023</v>
       </c>
       <c r="G2" s="5">
-        <v>98882.680879166801</v>
+        <v>98847.359661897906</v>
       </c>
       <c r="H2" s="6">
-        <v>0.98710557519521103</v>
+        <v>0.98668067251851199</v>
       </c>
       <c r="I2" s="5">
-        <v>7393245.5461790496</v>
+        <v>7349359.7035207497</v>
       </c>
       <c r="J2" s="7">
-        <v>73.932455461790497</v>
+        <v>73.4935970352075</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -548,31 +548,31 @@
         <v>1</v>
       </c>
       <c r="B3" s="4">
-        <v>5.1676750327655195E-4</v>
+        <v>5.3565697743504005E-4</v>
       </c>
       <c r="C3" s="4">
-        <v>1.61649328166527</v>
+        <v>1.61529262224458</v>
       </c>
       <c r="D3" s="4">
-        <v>2.0645270962358899E-3</v>
+        <v>2.1398944403679498E-3</v>
       </c>
       <c r="E3" s="5">
-        <v>98789.057328736904</v>
+        <v>98749.224016469801</v>
       </c>
       <c r="F3" s="5">
-        <v>203.95268566678001</v>
+        <v>211.31291546349499</v>
       </c>
       <c r="G3" s="5">
-        <v>394670.10671843903</v>
+        <v>394492.97659735801</v>
       </c>
       <c r="H3" s="6">
-        <v>0.99816205045397499</v>
+        <v>0.99809583366926002</v>
       </c>
       <c r="I3" s="5">
-        <v>7294362.8652998796</v>
+        <v>7250512.3438588502</v>
       </c>
       <c r="J3" s="7">
-        <v>73.837761615911404</v>
+        <v>73.423486777471595</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -580,31 +580,31 @@
         <v>5</v>
       </c>
       <c r="B4" s="4">
-        <v>2.1518077519554701E-4</v>
+        <v>2.2203796746922099E-4</v>
       </c>
       <c r="C4" s="4">
-        <v>2.3600004886203498</v>
+        <v>2.3601316289226699</v>
       </c>
       <c r="D4" s="4">
-        <v>1.0752930265890499E-3</v>
+        <v>1.1095394796622399E-3</v>
       </c>
       <c r="E4" s="5">
-        <v>98585.104643070095</v>
+        <v>98537.911101006306</v>
       </c>
       <c r="F4" s="5">
-        <v>106.007875548239</v>
+        <v>109.331702610012</v>
       </c>
       <c r="G4" s="5">
-        <v>492645.66247570101</v>
+        <v>492400.93420135498</v>
       </c>
       <c r="H4" s="6">
-        <v>0.99889862371424099</v>
+        <v>0.99886100776116304</v>
       </c>
       <c r="I4" s="5">
-        <v>6899692.75858144</v>
+        <v>6856019.3672614899</v>
       </c>
       <c r="J4" s="7">
-        <v>69.987172844842604</v>
+        <v>69.577478258431199</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -612,31 +612,31 @@
         <v>10</v>
       </c>
       <c r="B5" s="4">
-        <v>2.73483014384835E-4</v>
+        <v>2.83667726845968E-4</v>
       </c>
       <c r="C5" s="4">
-        <v>2.8272727661712</v>
+        <v>2.8296627477250298</v>
       </c>
       <c r="D5" s="4">
-        <v>1.3666030309458701E-3</v>
+        <v>1.41746596473892E-3</v>
       </c>
       <c r="E5" s="5">
-        <v>98479.0967675219</v>
+        <v>98428.579398396294</v>
       </c>
       <c r="F5" s="5">
-        <v>134.581832127296</v>
+        <v>139.519161254837</v>
       </c>
       <c r="G5" s="5">
-        <v>492103.07422576798</v>
+        <v>491840.09335890401</v>
       </c>
       <c r="H5" s="6">
-        <v>0.99703396144692302</v>
+        <v>0.99691048365676604</v>
       </c>
       <c r="I5" s="5">
-        <v>6407047.0961057404</v>
+        <v>6363618.4330601403</v>
       </c>
       <c r="J5" s="7">
-        <v>65.059970150119895</v>
+        <v>64.652141399938003</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -644,31 +644,31 @@
         <v>15</v>
       </c>
       <c r="B6" s="4">
-        <v>1.0380742546817201E-3</v>
+        <v>1.08362399986354E-3</v>
       </c>
       <c r="C6" s="4">
-        <v>2.8813164627263999</v>
+        <v>2.8831038757430498</v>
       </c>
       <c r="D6" s="4">
-        <v>5.1789808774971502E-3</v>
+        <v>5.40571971374962E-3</v>
       </c>
       <c r="E6" s="5">
-        <v>98344.514935394604</v>
+        <v>98289.060237141399</v>
       </c>
       <c r="F6" s="5">
-        <v>509.32436225714599</v>
+        <v>531.32311056983599</v>
       </c>
       <c r="G6" s="5">
-        <v>490643.47753552598</v>
+        <v>490320.54535221402</v>
       </c>
       <c r="H6" s="6">
-        <v>0.99294265691655104</v>
+        <v>0.99262130110337998</v>
       </c>
       <c r="I6" s="5">
-        <v>5914944.0218799701</v>
+        <v>5871778.33970124</v>
       </c>
       <c r="J6" s="7">
-        <v>60.145133928065803</v>
+        <v>59.739897049930399</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -676,31 +676,31 @@
         <v>20</v>
       </c>
       <c r="B7" s="4">
-        <v>1.72320167588012E-3</v>
+        <v>1.80359724830181E-3</v>
       </c>
       <c r="C7" s="4">
-        <v>2.6234795367760602</v>
+        <v>2.6235690268902898</v>
       </c>
       <c r="D7" s="4">
-        <v>8.5808678032458403E-3</v>
+        <v>8.9794989921035493E-3</v>
       </c>
       <c r="E7" s="5">
-        <v>97835.190573137501</v>
+        <v>97757.737126571606</v>
       </c>
       <c r="F7" s="5">
-        <v>839.51083681345301</v>
+        <v>877.81550199836795</v>
       </c>
       <c r="G7" s="5">
-        <v>487180.83818290202</v>
+        <v>486702.61768523301</v>
       </c>
       <c r="H7" s="6">
-        <v>0.99081922974080505</v>
+        <v>0.99039820432553705</v>
       </c>
       <c r="I7" s="5">
-        <v>5424300.5443444503</v>
+        <v>5381457.7943490203</v>
       </c>
       <c r="J7" s="7">
-        <v>55.443246060725698</v>
+        <v>55.048919426003003</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -708,31 +708,31 @@
         <v>25</v>
       </c>
       <c r="B8" s="4">
-        <v>1.9103779685442799E-3</v>
+        <v>1.99666498417421E-3</v>
       </c>
       <c r="C8" s="4">
-        <v>2.5380973420464801</v>
+        <v>2.5373198413822999</v>
       </c>
       <c r="D8" s="4">
-        <v>9.5071760289905903E-3</v>
+        <v>9.9344756413908102E-3</v>
       </c>
       <c r="E8" s="5">
-        <v>96995.679736324004</v>
+        <v>96879.921624573195</v>
       </c>
       <c r="F8" s="5">
-        <v>922.15500130482496</v>
+        <v>962.45122151917894</v>
       </c>
       <c r="G8" s="5">
-        <v>482708.14283286303</v>
+        <v>482029.398595993</v>
       </c>
       <c r="H8" s="6">
-        <v>0.99004174457302796</v>
+        <v>0.989602694551455</v>
       </c>
       <c r="I8" s="5">
-        <v>4937119.7061615502</v>
+        <v>4894755.1766637899</v>
       </c>
       <c r="J8" s="7">
-        <v>50.9004083437815</v>
+        <v>50.5239382380162</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -740,31 +740,31 @@
         <v>30</v>
       </c>
       <c r="B9" s="4">
-        <v>2.1088758256744698E-3</v>
+        <v>2.20094107523422E-3</v>
       </c>
       <c r="C9" s="4">
-        <v>2.5527606134387399</v>
+        <v>2.5523472376768299</v>
       </c>
       <c r="D9" s="4">
-        <v>1.0490239798221199E-2</v>
+        <v>1.09457391523991E-2</v>
       </c>
       <c r="E9" s="5">
-        <v>96073.524735019193</v>
+        <v>95917.470403054002</v>
       </c>
       <c r="F9" s="5">
-        <v>1007.83431273069</v>
+        <v>1049.88761118978</v>
       </c>
       <c r="G9" s="5">
-        <v>477901.21184985299</v>
+        <v>477017.591703613</v>
       </c>
       <c r="H9" s="6">
-        <v>0.98862818862395196</v>
+        <v>0.98813265536795303</v>
       </c>
       <c r="I9" s="5">
-        <v>4454411.5633286797</v>
+        <v>4412725.77806779</v>
       </c>
       <c r="J9" s="7">
-        <v>46.3646106002087</v>
+        <v>46.00544363321</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -772,31 +772,31 @@
         <v>35</v>
       </c>
       <c r="B10" s="4">
-        <v>2.5134110497727E-3</v>
+        <v>2.6241431728292498E-3</v>
       </c>
       <c r="C10" s="4">
-        <v>2.5900328765763199</v>
+        <v>2.5897512553256998</v>
       </c>
       <c r="D10" s="4">
-        <v>1.24913919151124E-2</v>
+        <v>1.3038251041268999E-2</v>
       </c>
       <c r="E10" s="5">
-        <v>95065.690422288506</v>
+        <v>94867.582791864304</v>
       </c>
       <c r="F10" s="5">
-        <v>1187.5027967455501</v>
+        <v>1236.9073601186999</v>
       </c>
       <c r="G10" s="5">
-        <v>472466.60941231198</v>
+        <v>471356.65954731702</v>
       </c>
       <c r="H10" s="6">
-        <v>0.98567350068275605</v>
+        <v>0.98505025063598906</v>
       </c>
       <c r="I10" s="5">
-        <v>3976510.35147883</v>
+        <v>3935708.1863641799</v>
       </c>
       <c r="J10" s="7">
-        <v>41.829079805920401</v>
+        <v>41.486333587722697</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
@@ -804,31 +804,31 @@
         <v>40</v>
       </c>
       <c r="B11" s="4">
-        <v>3.33158091149461E-3</v>
+        <v>3.4761747785743398E-3</v>
       </c>
       <c r="C11" s="4">
-        <v>2.61965996059046</v>
+        <v>2.6187562035739398</v>
       </c>
       <c r="D11" s="4">
-        <v>1.6526841819187101E-2</v>
+        <v>1.7238182772821499E-2</v>
       </c>
       <c r="E11" s="5">
-        <v>93878.187625542894</v>
+        <v>93630.675431745607</v>
       </c>
       <c r="F11" s="5">
-        <v>1551.50995715932</v>
+        <v>1614.0226962351601</v>
       </c>
       <c r="G11" s="5">
-        <v>465697.81685514603</v>
+        <v>464309.995626027</v>
       </c>
       <c r="H11" s="6">
-        <v>0.98059955434850399</v>
+        <v>0.97978957690055202</v>
       </c>
       <c r="I11" s="5">
-        <v>3504043.7420665198</v>
+        <v>3464351.5268168701</v>
       </c>
       <c r="J11" s="7">
-        <v>37.325430227128898</v>
+        <v>37.000176607102397</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -836,31 +836,31 @@
         <v>45</v>
       </c>
       <c r="B12" s="4">
-        <v>4.6150579948923496E-3</v>
+        <v>4.8044662658734997E-3</v>
       </c>
       <c r="C12" s="4">
-        <v>2.64163509617828</v>
+        <v>2.6404705084682201</v>
       </c>
       <c r="D12" s="4">
-        <v>2.2826842827042001E-2</v>
+        <v>2.3753059994090001E-2</v>
       </c>
       <c r="E12" s="5">
-        <v>92326.677668383607</v>
+        <v>92016.652735510404</v>
       </c>
       <c r="F12" s="5">
-        <v>2107.5265598791598</v>
+        <v>2185.6770728819101</v>
       </c>
       <c r="G12" s="5">
-        <v>456663.07166922698</v>
+        <v>454926.09416512202</v>
       </c>
       <c r="H12" s="6">
-        <v>0.97210003416769897</v>
+        <v>0.97099339669260498</v>
       </c>
       <c r="I12" s="5">
-        <v>3038345.92521137</v>
+        <v>3000041.5311908401</v>
       </c>
       <c r="J12" s="7">
-        <v>32.908645712612099</v>
+        <v>32.603245630049798</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
@@ -868,31 +868,31 @@
         <v>50</v>
       </c>
       <c r="B13" s="4">
-        <v>6.8856943800733299E-3</v>
+        <v>7.1580356370831398E-3</v>
       </c>
       <c r="C13" s="4">
-        <v>2.6531754487203298</v>
+        <v>2.6518561102064599</v>
       </c>
       <c r="D13" s="4">
-        <v>3.3880971773759302E-2</v>
+        <v>3.5198557395774599E-2</v>
       </c>
       <c r="E13" s="5">
-        <v>90219.151108504506</v>
+        <v>89830.975662628494</v>
       </c>
       <c r="F13" s="5">
-        <v>3056.7125121597601</v>
+        <v>3161.9207527794601</v>
       </c>
       <c r="G13" s="5">
-        <v>443922.18757278199</v>
+        <v>441730.23341749201</v>
       </c>
       <c r="H13" s="6">
-        <v>0.95843156219442704</v>
+        <v>0.95687279819052096</v>
       </c>
       <c r="I13" s="5">
-        <v>2581682.8535421402</v>
+        <v>2545115.4370257198</v>
       </c>
       <c r="J13" s="7">
-        <v>28.6156854927311</v>
+        <v>28.332269779460201</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
@@ -900,31 +900,31 @@
         <v>55</v>
       </c>
       <c r="B14" s="4">
-        <v>1.03131886967019E-2</v>
+        <v>1.06977735749771E-2</v>
       </c>
       <c r="C14" s="4">
-        <v>2.64282294691129</v>
+        <v>2.6412507193885499</v>
       </c>
       <c r="D14" s="4">
-        <v>5.0342125813953698E-2</v>
+        <v>5.2172383052619897E-2</v>
       </c>
       <c r="E14" s="5">
-        <v>87162.438596344698</v>
+        <v>86669.054909849001</v>
       </c>
       <c r="F14" s="5">
-        <v>4387.9424500681898</v>
+        <v>4521.7311315651896</v>
       </c>
       <c r="G14" s="5">
-        <v>425469.035728149</v>
+        <v>422679.64449554699</v>
       </c>
       <c r="H14" s="6">
-        <v>0.93912655713506199</v>
+        <v>0.93697672245215902</v>
       </c>
       <c r="I14" s="5">
-        <v>2137760.6659693602</v>
+        <v>2103385.20360822</v>
       </c>
       <c r="J14" s="7">
-        <v>24.526168615697902</v>
+        <v>24.269160495589901</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
@@ -932,31 +932,31 @@
         <v>60</v>
       </c>
       <c r="B15" s="4">
-        <v>1.5151931465141299E-2</v>
+        <v>1.5693031805452399E-2</v>
       </c>
       <c r="C15" s="4">
-        <v>2.6374911828963801</v>
+        <v>2.6354895010124899</v>
       </c>
       <c r="D15" s="4">
-        <v>7.3141444369373101E-2</v>
+        <v>7.5657775984092096E-2</v>
       </c>
       <c r="E15" s="5">
-        <v>82774.496146276506</v>
+        <v>82147.323778283797</v>
       </c>
       <c r="F15" s="5">
-        <v>6054.2462050857703</v>
+        <v>6215.0838201100696</v>
       </c>
       <c r="G15" s="5">
-        <v>399569.27069095097</v>
+        <v>396040.98794668203</v>
       </c>
       <c r="H15" s="6">
-        <v>0.90961458300748299</v>
+        <v>0.90665920054982896</v>
       </c>
       <c r="I15" s="5">
-        <v>1712291.6302412101</v>
+        <v>1680705.5591126799</v>
       </c>
       <c r="J15" s="7">
-        <v>20.686222326443499</v>
+        <v>20.459650805532199</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
@@ -964,31 +964,31 @@
         <v>65</v>
       </c>
       <c r="B16" s="4">
-        <v>2.3217365803874599E-2</v>
+        <v>2.3982288185489802E-2</v>
       </c>
       <c r="C16" s="4">
-        <v>2.6124495144659798</v>
+        <v>2.6093383320991199</v>
       </c>
       <c r="D16" s="4">
-        <v>0.10998980455023299</v>
+        <v>0.113409285455306</v>
       </c>
       <c r="E16" s="5">
-        <v>76720.249941190705</v>
+        <v>75932.239958173799</v>
       </c>
       <c r="F16" s="5">
-        <v>8438.4452960766193</v>
+        <v>8611.4210766773595</v>
       </c>
       <c r="G16" s="5">
-        <v>363454.03554215399</v>
+        <v>359074.20551670302</v>
       </c>
       <c r="H16" s="6">
-        <v>0.87056448962134303</v>
+        <v>0.86688847644262301</v>
       </c>
       <c r="I16" s="5">
-        <v>1312722.35955026</v>
+        <v>1284664.5711660001</v>
       </c>
       <c r="J16" s="7">
-        <v>17.110506816082101</v>
+        <v>16.918565445634599</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
@@ -996,31 +996,31 @@
         <v>70</v>
       </c>
       <c r="B17" s="4">
-        <v>3.2787893306782903E-2</v>
+        <v>3.3712330333774597E-2</v>
       </c>
       <c r="C17" s="4">
-        <v>2.5903386649681002</v>
+        <v>2.5865174216084799</v>
       </c>
       <c r="D17" s="4">
-        <v>0.151935397387649</v>
+        <v>0.15587871675162601</v>
       </c>
       <c r="E17" s="5">
-        <v>68281.804645114098</v>
+        <v>67320.818881496394</v>
       </c>
       <c r="F17" s="5">
-        <v>10374.4231231012</v>
+        <v>10493.8828579163</v>
       </c>
       <c r="G17" s="5">
-        <v>316410.17695257301</v>
+        <v>311277.29095022002</v>
       </c>
       <c r="H17" s="6">
-        <v>0.81672413495096097</v>
+        <v>0.812480984658278</v>
       </c>
       <c r="I17" s="5">
-        <v>949268.32400810905</v>
+        <v>925590.36564929294</v>
       </c>
       <c r="J17" s="7">
-        <v>13.9022149303436</v>
+        <v>13.748946923515501</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
@@ -1028,31 +1028,31 @@
         <v>75</v>
       </c>
       <c r="B18" s="4">
-        <v>4.9719889769274703E-2</v>
+        <v>5.0892852570503903E-2</v>
       </c>
       <c r="C18" s="4">
-        <v>2.5781745439402899</v>
+        <v>2.5738147658055301</v>
       </c>
       <c r="D18" s="4">
-        <v>0.22188199548475601</v>
+        <v>0.22649738752558801</v>
       </c>
       <c r="E18" s="5">
-        <v>57907.381522012904</v>
+        <v>56826.9360235801</v>
       </c>
       <c r="F18" s="5">
-        <v>12848.605365401299</v>
+        <v>12871.1525504246</v>
       </c>
       <c r="G18" s="5">
-        <v>258419.82806127</v>
+        <v>252906.879852996</v>
       </c>
       <c r="H18" s="6">
-        <v>0.73023469920203699</v>
+        <v>0.72544334283935896</v>
       </c>
       <c r="I18" s="5">
-        <v>632858.14705553697</v>
+        <v>614313.07469907298</v>
       </c>
       <c r="J18" s="7">
-        <v>10.928799238054999</v>
+        <v>10.8102445369246</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
@@ -1060,31 +1060,31 @@
         <v>80</v>
       </c>
       <c r="B19" s="4">
-        <v>7.8452712077509104E-2</v>
+        <v>7.9926147918227594E-2</v>
       </c>
       <c r="C19" s="4">
-        <v>2.5286876700126801</v>
+        <v>2.52391864129295</v>
       </c>
       <c r="D19" s="4">
-        <v>0.32856164857825498</v>
+        <v>0.33360841773988797</v>
       </c>
       <c r="E19" s="5">
-        <v>45058.776156611602</v>
+        <v>43955.783473155498</v>
       </c>
       <c r="F19" s="5">
-        <v>14804.5857769349</v>
+        <v>14664.0193749965</v>
       </c>
       <c r="G19" s="5">
-        <v>188707.12541216399</v>
+        <v>183469.61234762901</v>
       </c>
       <c r="H19" s="6">
-        <v>0.60828781286322797</v>
+        <v>0.60320281407905896</v>
       </c>
       <c r="I19" s="5">
-        <v>374438.31899426598</v>
+        <v>361406.19484607701</v>
       </c>
       <c r="J19" s="7">
-        <v>8.3099975394987293</v>
+        <v>8.22203965643779</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
@@ -1092,31 +1092,31 @@
         <v>85</v>
       </c>
       <c r="B20" s="4">
-        <v>0.12503991251365701</v>
+        <v>0.12695001801706801</v>
       </c>
       <c r="C20" s="4">
-        <v>2.45820229405625</v>
+        <v>2.4526151514869898</v>
       </c>
       <c r="D20" s="4">
-        <v>0.47441732470241699</v>
+        <v>0.47963927876540002</v>
       </c>
       <c r="E20" s="5">
-        <v>30254.1903796767</v>
+        <v>29291.764098159001</v>
       </c>
       <c r="F20" s="5">
-        <v>14353.1120609638</v>
+        <v>14049.480605807201</v>
       </c>
       <c r="G20" s="5">
-        <v>114788.24458867199</v>
+        <v>110669.386466084</v>
       </c>
       <c r="H20" s="6">
-        <v>0.38196571951749297</v>
+        <v>0.37804028316071803</v>
       </c>
       <c r="I20" s="5">
-        <v>185731.19358210301</v>
+        <v>177936.582498448</v>
       </c>
       <c r="J20" s="7">
-        <v>6.13902376005632</v>
+        <v>6.0746284143955496</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
@@ -1124,31 +1124,31 @@
         <v>90</v>
       </c>
       <c r="B21" s="4">
-        <v>0.224138953121125</v>
+        <v>0.226593115090131</v>
       </c>
       <c r="C21" s="4">
-        <v>4.4615181166640001</v>
+        <v>4.4131967540242103</v>
       </c>
       <c r="D21" s="4">
         <v>1</v>
       </c>
       <c r="E21" s="5">
-        <v>15901.0783187129</v>
+        <v>15242.2834923518</v>
       </c>
       <c r="F21" s="5">
-        <v>15901.0783187129</v>
+        <v>15242.2834923518</v>
       </c>
       <c r="G21" s="5">
-        <v>70942.948993430604</v>
+        <v>67267.196032363601</v>
       </c>
       <c r="H21" s="6">
         <v>0</v>
       </c>
       <c r="I21" s="5">
-        <v>70942.948993430604</v>
+        <v>67267.196032363601</v>
       </c>
       <c r="J21" s="7">
-        <v>4.4615181166640001</v>
+        <v>4.4131967540242103</v>
       </c>
     </row>
   </sheetData>
